--- a/private_credit_template.xlsx
+++ b/private_credit_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29504"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29509"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\PrivateCredit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBCE062E-502B-4855-89DC-F24798BA3FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A81BE7-9508-46F4-ADD3-D8DCAAE15088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="828" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GC" sheetId="15" r:id="rId1"/>
@@ -728,68 +728,6 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Ján Pitoňák</author>
-  </authors>
-  <commentList>
-    <comment ref="I86" authorId="0" shapeId="0" xr:uid="{1CB47F51-9680-483D-B01B-0FFC4FAC2EC1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t>Ján Pitoňák:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t xml:space="preserve">
-Fixed amount at 15k</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I87" authorId="0" shapeId="0" xr:uid="{A4A67227-954B-4BC5-91AD-B19006C37B8A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t>Ján Pitoňák:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="238"/>
-          </rPr>
-          <t xml:space="preserve">
-1% of Amount - Engagement fee</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="186">
   <si>
@@ -1369,7 +1307,7 @@
     <numFmt numFmtId="173" formatCode="0.000%"/>
     <numFmt numFmtId="174" formatCode="0.0"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="57" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1778,21 +1716,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="238"/>
     </font>
   </fonts>
   <fills count="9">
@@ -3434,6 +3357,15 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="10" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="6" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -3442,12 +3374,6 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="6" borderId="60" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="41" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -3458,6 +3384,12 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="60" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="41" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="7" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -3466,15 +3398,6 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="7" borderId="60" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -9793,7 +9716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B737DBEE-F79B-4056-A95F-1EB5684148D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B737DBEE-F79B-4056-A95F-1EB5684148D4}">
   <sheetPr>
     <tabColor rgb="FFE83E33"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
@@ -9990,15 +9913,15 @@
       <c r="J3" s="14"/>
       <c r="K3" s="33"/>
       <c r="L3" s="14"/>
-      <c r="M3" s="359" t="s">
+      <c r="M3" s="365" t="s">
         <v>103</v>
       </c>
-      <c r="N3" s="360"/>
+      <c r="N3" s="366"/>
       <c r="O3" s="14"/>
-      <c r="P3" s="359" t="s">
+      <c r="P3" s="365" t="s">
         <v>104</v>
       </c>
-      <c r="Q3" s="360"/>
+      <c r="Q3" s="366"/>
       <c r="T3" s="14"/>
       <c r="U3" s="118"/>
       <c r="V3" s="119"/>
@@ -11410,7 +11333,7 @@
     <row r="25" spans="1:61" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
       <c r="B25" s="14"/>
-      <c r="C25" s="361" t="s">
+      <c r="C25" s="362" t="s">
         <v>156</v>
       </c>
       <c r="D25" s="261" t="s">
@@ -11472,12 +11395,12 @@
     <row r="26" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
-      <c r="C26" s="362"/>
+      <c r="C26" s="363"/>
       <c r="D26" s="228" t="s">
         <v>34</v>
       </c>
       <c r="E26" s="229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="230" t="s">
         <v>70</v>
@@ -11534,7 +11457,7 @@
     <row r="27" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
-      <c r="C27" s="362"/>
+      <c r="C27" s="363"/>
       <c r="D27" s="228" t="s">
         <v>33</v>
       </c>
@@ -11596,12 +11519,12 @@
     <row r="28" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
-      <c r="C28" s="362"/>
+      <c r="C28" s="363"/>
       <c r="D28" s="228" t="s">
         <v>32</v>
       </c>
       <c r="E28" s="229">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="F28" s="230" t="s">
         <v>70</v>
@@ -11658,7 +11581,7 @@
     <row r="29" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
-      <c r="C29" s="362"/>
+      <c r="C29" s="363"/>
       <c r="D29" s="228" t="s">
         <v>31</v>
       </c>
@@ -11720,7 +11643,7 @@
     <row r="30" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
-      <c r="C30" s="362"/>
+      <c r="C30" s="363"/>
       <c r="D30" s="228" t="s">
         <v>158</v>
       </c>
@@ -11782,12 +11705,12 @@
     <row r="31" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
-      <c r="C31" s="362"/>
+      <c r="C31" s="363"/>
       <c r="D31" s="274" t="s">
         <v>160</v>
       </c>
       <c r="E31" s="231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="276"/>
       <c r="G31" s="14"/>
@@ -11842,7 +11765,7 @@
     <row r="32" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
-      <c r="C32" s="362"/>
+      <c r="C32" s="363"/>
       <c r="D32" s="243" t="s">
         <v>101</v>
       </c>
@@ -11904,7 +11827,7 @@
     <row r="33" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="362"/>
+      <c r="C33" s="363"/>
       <c r="D33" s="243" t="s">
         <v>153</v>
       </c>
@@ -11966,12 +11889,12 @@
     <row r="34" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14"/>
       <c r="B34" s="183"/>
-      <c r="C34" s="362"/>
+      <c r="C34" s="363"/>
       <c r="D34" s="274" t="s">
         <v>154</v>
       </c>
       <c r="E34" s="208">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F34" s="232" t="s">
         <v>28</v>
@@ -12028,12 +11951,12 @@
     <row r="35" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="183"/>
-      <c r="C35" s="362"/>
+      <c r="C35" s="363"/>
       <c r="D35" s="273" t="s">
         <v>155</v>
       </c>
       <c r="E35" s="231">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="F35" s="209" t="s">
         <v>114</v>
@@ -12090,7 +12013,7 @@
     <row r="36" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
       <c r="B36" s="183"/>
-      <c r="C36" s="362"/>
+      <c r="C36" s="363"/>
       <c r="D36" s="264" t="s">
         <v>105</v>
       </c>
@@ -12152,7 +12075,7 @@
     <row r="37" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14"/>
       <c r="B37" s="183"/>
-      <c r="C37" s="362"/>
+      <c r="C37" s="363"/>
       <c r="D37" s="226" t="s">
         <v>96</v>
       </c>
@@ -12214,7 +12137,7 @@
     <row r="38" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14"/>
       <c r="B38" s="183"/>
-      <c r="C38" s="362"/>
+      <c r="C38" s="363"/>
       <c r="D38" s="240" t="s">
         <v>97</v>
       </c>
@@ -12280,7 +12203,7 @@
     <row r="39" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14"/>
       <c r="B39" s="183"/>
-      <c r="C39" s="362"/>
+      <c r="C39" s="363"/>
       <c r="D39" s="243" t="s">
         <v>137</v>
       </c>
@@ -12345,7 +12268,7 @@
     <row r="40" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14"/>
       <c r="B40" s="183"/>
-      <c r="C40" s="362"/>
+      <c r="C40" s="363"/>
       <c r="D40" s="243" t="s">
         <v>138</v>
       </c>
@@ -12410,7 +12333,7 @@
     <row r="41" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14"/>
       <c r="B41" s="183"/>
-      <c r="C41" s="362"/>
+      <c r="C41" s="363"/>
       <c r="D41" s="243" t="s">
         <v>123</v>
       </c>
@@ -12475,7 +12398,7 @@
     <row r="42" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14"/>
       <c r="B42" s="183"/>
-      <c r="C42" s="363"/>
+      <c r="C42" s="364"/>
       <c r="D42" s="244" t="s">
         <v>142</v>
       </c>
@@ -12542,7 +12465,7 @@
     <row r="43" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14"/>
       <c r="B43" s="183"/>
-      <c r="C43" s="356" t="s">
+      <c r="C43" s="359" t="s">
         <v>119</v>
       </c>
       <c r="D43" s="226" t="s">
@@ -12611,7 +12534,7 @@
     <row r="44" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14"/>
       <c r="B44" s="183"/>
-      <c r="C44" s="357"/>
+      <c r="C44" s="360"/>
       <c r="D44" s="243" t="s">
         <v>92</v>
       </c>
@@ -12678,7 +12601,7 @@
     <row r="45" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14"/>
       <c r="B45" s="183"/>
-      <c r="C45" s="357"/>
+      <c r="C45" s="360"/>
       <c r="D45" s="243" t="s">
         <v>115</v>
       </c>
@@ -12745,7 +12668,7 @@
     <row r="46" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14"/>
       <c r="B46" s="183"/>
-      <c r="C46" s="357"/>
+      <c r="C46" s="360"/>
       <c r="D46" s="243" t="s">
         <v>116</v>
       </c>
@@ -12812,12 +12735,12 @@
     <row r="47" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14"/>
       <c r="B47" s="183"/>
-      <c r="C47" s="358"/>
+      <c r="C47" s="361"/>
       <c r="D47" s="210" t="s">
         <v>117</v>
       </c>
       <c r="E47" s="201">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F47" s="245" t="s">
         <v>28</v>
@@ -12879,7 +12802,7 @@
     <row r="48" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14"/>
       <c r="B48" s="184"/>
-      <c r="C48" s="364" t="s">
+      <c r="C48" s="367" t="s">
         <v>120</v>
       </c>
       <c r="D48" s="350" t="s">
@@ -12946,7 +12869,7 @@
     <row r="49" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14"/>
       <c r="B49" s="184"/>
-      <c r="C49" s="365"/>
+      <c r="C49" s="368"/>
       <c r="D49" s="207" t="s">
         <v>129</v>
       </c>
@@ -13013,7 +12936,7 @@
     <row r="50" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="14"/>
       <c r="B50" s="184"/>
-      <c r="C50" s="366"/>
+      <c r="C50" s="369"/>
       <c r="D50" s="210" t="s">
         <v>128</v>
       </c>
@@ -13080,7 +13003,7 @@
     <row r="51" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14"/>
       <c r="B51" s="184"/>
-      <c r="C51" s="356" t="s">
+      <c r="C51" s="359" t="s">
         <v>84</v>
       </c>
       <c r="D51" s="280" t="s">
@@ -13149,7 +13072,7 @@
     <row r="52" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14"/>
       <c r="B52" s="184"/>
-      <c r="C52" s="357"/>
+      <c r="C52" s="360"/>
       <c r="D52" s="237" t="s">
         <v>107</v>
       </c>
@@ -13216,7 +13139,7 @@
     <row r="53" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14"/>
       <c r="B53" s="184"/>
-      <c r="C53" s="357"/>
+      <c r="C53" s="360"/>
       <c r="D53" s="237" t="s">
         <v>112</v>
       </c>
@@ -13281,7 +13204,7 @@
     <row r="54" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14"/>
       <c r="B54" s="184"/>
-      <c r="C54" s="357"/>
+      <c r="C54" s="360"/>
       <c r="D54" s="280" t="s">
         <v>110</v>
       </c>
@@ -13348,7 +13271,7 @@
     <row r="55" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
       <c r="B55" s="184"/>
-      <c r="C55" s="357"/>
+      <c r="C55" s="360"/>
       <c r="D55" s="237" t="s">
         <v>109</v>
       </c>
@@ -13415,7 +13338,7 @@
     <row r="56" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14"/>
       <c r="B56" s="184"/>
-      <c r="C56" s="358"/>
+      <c r="C56" s="361"/>
       <c r="D56" s="237" t="s">
         <v>113</v>
       </c>
@@ -13476,7 +13399,7 @@
     <row r="57" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
       <c r="B57" s="185"/>
-      <c r="C57" s="356" t="s">
+      <c r="C57" s="359" t="s">
         <v>69</v>
       </c>
       <c r="D57" s="270" t="s">
@@ -13541,7 +13464,7 @@
     <row r="58" spans="1:61" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
-      <c r="C58" s="357"/>
+      <c r="C58" s="360"/>
       <c r="D58" s="243" t="s">
         <v>162</v>
       </c>
@@ -13608,7 +13531,7 @@
     <row r="59" spans="1:61" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
-      <c r="C59" s="357"/>
+      <c r="C59" s="360"/>
       <c r="D59" s="243" t="s">
         <v>149</v>
       </c>
@@ -13675,7 +13598,7 @@
     <row r="60" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
       <c r="B60" s="14"/>
-      <c r="C60" s="357"/>
+      <c r="C60" s="360"/>
       <c r="D60" s="243" t="s">
         <v>16</v>
       </c>
@@ -13742,7 +13665,7 @@
     <row r="61" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
       <c r="B61" s="14"/>
-      <c r="C61" s="357"/>
+      <c r="C61" s="360"/>
       <c r="D61" s="243" t="s">
         <v>148</v>
       </c>
@@ -13809,7 +13732,7 @@
     <row r="62" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A62" s="14"/>
       <c r="B62" s="14"/>
-      <c r="C62" s="357"/>
+      <c r="C62" s="360"/>
       <c r="D62" s="243" t="s">
         <v>67</v>
       </c>
@@ -13876,7 +13799,7 @@
     <row r="63" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A63" s="14"/>
       <c r="B63" s="14"/>
-      <c r="C63" s="357"/>
+      <c r="C63" s="360"/>
       <c r="D63" s="243" t="s">
         <v>17</v>
       </c>
@@ -13943,7 +13866,7 @@
     <row r="64" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
-      <c r="C64" s="357"/>
+      <c r="C64" s="360"/>
       <c r="D64" s="273" t="s">
         <v>80</v>
       </c>
@@ -14008,7 +13931,7 @@
     <row r="65" spans="1:61" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="14"/>
       <c r="B65" s="14"/>
-      <c r="C65" s="358"/>
+      <c r="C65" s="361"/>
       <c r="D65" s="244" t="s">
         <v>151</v>
       </c>
@@ -14531,7 +14454,7 @@
     <row r="73" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A73" s="9"/>
       <c r="B73" s="14"/>
-      <c r="C73" s="356" t="s">
+      <c r="C73" s="359" t="s">
         <v>19</v>
       </c>
       <c r="D73" s="226" t="s">
@@ -14598,7 +14521,7 @@
     <row r="74" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A74" s="9"/>
       <c r="B74" s="14"/>
-      <c r="C74" s="357"/>
+      <c r="C74" s="360"/>
       <c r="D74" s="226" t="s">
         <v>81</v>
       </c>
@@ -14663,7 +14586,7 @@
     <row r="75" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A75" s="9"/>
       <c r="B75" s="14"/>
-      <c r="C75" s="357"/>
+      <c r="C75" s="360"/>
       <c r="D75" s="226" t="s">
         <v>83</v>
       </c>
@@ -14728,7 +14651,7 @@
     <row r="76" spans="1:61" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
       <c r="B76" s="14"/>
-      <c r="C76" s="357"/>
+      <c r="C76" s="360"/>
       <c r="D76" s="226" t="s">
         <v>132</v>
       </c>
@@ -14860,7 +14783,7 @@
     <row r="78" spans="1:61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9"/>
       <c r="B78" s="14"/>
-      <c r="C78" s="361" t="s">
+      <c r="C78" s="362" t="s">
         <v>72</v>
       </c>
       <c r="D78" s="39" t="s">
@@ -14927,7 +14850,7 @@
     <row r="79" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9"/>
       <c r="B79" s="14"/>
-      <c r="C79" s="362"/>
+      <c r="C79" s="363"/>
       <c r="D79" s="39" t="s">
         <v>162</v>
       </c>
@@ -14992,7 +14915,7 @@
     <row r="80" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9"/>
       <c r="B80" s="14"/>
-      <c r="C80" s="362"/>
+      <c r="C80" s="363"/>
       <c r="D80" s="39" t="s">
         <v>149</v>
       </c>
@@ -15057,7 +14980,7 @@
     <row r="81" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9"/>
       <c r="B81" s="14"/>
-      <c r="C81" s="362"/>
+      <c r="C81" s="363"/>
       <c r="D81" s="39" t="s">
         <v>16</v>
       </c>
@@ -15122,7 +15045,7 @@
     <row r="82" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="9"/>
       <c r="B82" s="14"/>
-      <c r="C82" s="362"/>
+      <c r="C82" s="363"/>
       <c r="D82" s="39" t="s">
         <v>148</v>
       </c>
@@ -15193,7 +15116,7 @@
     <row r="83" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9"/>
       <c r="B83" s="14"/>
-      <c r="C83" s="362"/>
+      <c r="C83" s="363"/>
       <c r="D83" s="39" t="s">
         <v>67</v>
       </c>
@@ -15261,7 +15184,7 @@
     <row r="84" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9"/>
       <c r="B84" s="14"/>
-      <c r="C84" s="362"/>
+      <c r="C84" s="363"/>
       <c r="D84" s="39" t="s">
         <v>17</v>
       </c>
@@ -15329,7 +15252,7 @@
     <row r="85" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9"/>
       <c r="B85" s="14"/>
-      <c r="C85" s="362"/>
+      <c r="C85" s="363"/>
       <c r="D85" s="39" t="s">
         <v>79</v>
       </c>
@@ -15397,7 +15320,7 @@
     <row r="86" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9"/>
       <c r="B86" s="14"/>
-      <c r="C86" s="363"/>
+      <c r="C86" s="364"/>
       <c r="D86" s="39" t="s">
         <v>151</v>
       </c>
@@ -15410,9 +15333,7 @@
       <c r="H86" s="314" t="s">
         <v>164</v>
       </c>
-      <c r="I86" s="315">
-        <v>15000</v>
-      </c>
+      <c r="I86" s="315"/>
       <c r="J86" s="14"/>
       <c r="K86" s="33"/>
       <c r="L86" s="14"/>
@@ -15485,10 +15406,7 @@
       <c r="H87" s="316" t="s">
         <v>170</v>
       </c>
-      <c r="I87" s="317">
-        <f>1%*E72-I86</f>
-        <v>-15000</v>
-      </c>
+      <c r="I87" s="317"/>
       <c r="J87" s="14"/>
       <c r="K87" s="33"/>
       <c r="L87" s="14"/>
@@ -15613,7 +15531,7 @@
     <row r="89" spans="1:61" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9"/>
       <c r="B89" s="14"/>
-      <c r="C89" s="361" t="s">
+      <c r="C89" s="362" t="s">
         <v>73</v>
       </c>
       <c r="D89" s="110" t="str">
@@ -15688,7 +15606,7 @@
     <row r="90" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9"/>
       <c r="B90" s="14"/>
-      <c r="C90" s="362"/>
+      <c r="C90" s="363"/>
       <c r="D90" s="113" t="str">
         <f>"Net Break Event Point (after tax"&amp;IF($E$115&lt;&gt;0," and carry)",")")</f>
         <v>Net Break Event Point (after tax)</v>
@@ -15763,7 +15681,7 @@
     <row r="91" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A91" s="9"/>
       <c r="B91" s="14"/>
-      <c r="C91" s="362"/>
+      <c r="C91" s="363"/>
       <c r="D91" s="100" t="str">
         <f>"Net Multiple (after tax"&amp;IF($E$115&lt;&gt;0," and carry)",")")</f>
         <v>Net Multiple (after tax)</v>
@@ -15837,7 +15755,7 @@
     <row r="92" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A92" s="36"/>
       <c r="B92" s="14"/>
-      <c r="C92" s="362"/>
+      <c r="C92" s="363"/>
       <c r="D92" s="103" t="str">
         <f>"Net Profit (after tax"&amp;IF($E$115&lt;&gt;0," and carry)",")")</f>
         <v>Net Profit (after tax)</v>
@@ -15913,7 +15831,7 @@
     <row r="93" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9"/>
       <c r="B93" s="14"/>
-      <c r="C93" s="362"/>
+      <c r="C93" s="363"/>
       <c r="D93" s="102" t="str">
         <f>"Net Collections (after tax"&amp;IF($E$115&lt;&gt;0," and carry)",")")</f>
         <v>Net Collections (after tax)</v>
@@ -15990,7 +15908,7 @@
     <row r="94" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9"/>
       <c r="B94" s="42"/>
-      <c r="C94" s="362"/>
+      <c r="C94" s="363"/>
       <c r="D94" s="102" t="s">
         <v>53</v>
       </c>
@@ -16067,7 +15985,7 @@
     <row r="95" spans="1:61" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9"/>
       <c r="B95" s="42"/>
-      <c r="C95" s="362"/>
+      <c r="C95" s="363"/>
       <c r="D95" s="102" t="s">
         <v>131</v>
       </c>
@@ -16140,7 +16058,7 @@
     <row r="96" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9"/>
       <c r="B96" s="42"/>
-      <c r="C96" s="362"/>
+      <c r="C96" s="363"/>
       <c r="D96" s="102" t="s">
         <v>136</v>
       </c>
@@ -16210,7 +16128,7 @@
     <row r="97" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="9"/>
       <c r="B97" s="42"/>
-      <c r="C97" s="362"/>
+      <c r="C97" s="363"/>
       <c r="D97" s="204" t="s">
         <v>135</v>
       </c>
@@ -16278,7 +16196,7 @@
     <row r="98" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="9"/>
       <c r="B98" s="42"/>
-      <c r="C98" s="362"/>
+      <c r="C98" s="363"/>
       <c r="D98" s="102" t="s">
         <v>157</v>
       </c>
@@ -16349,7 +16267,7 @@
     <row r="99" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9"/>
       <c r="B99" s="42"/>
-      <c r="C99" s="362"/>
+      <c r="C99" s="363"/>
       <c r="D99" s="102" t="s">
         <v>8</v>
       </c>
@@ -16420,7 +16338,7 @@
     <row r="100" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="42"/>
-      <c r="C100" s="362"/>
+      <c r="C100" s="363"/>
       <c r="D100" s="102" t="s">
         <v>7</v>
       </c>
@@ -16491,7 +16409,7 @@
     <row r="101" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9"/>
       <c r="B101" s="42"/>
-      <c r="C101" s="362"/>
+      <c r="C101" s="363"/>
       <c r="D101" s="102" t="s">
         <v>158</v>
       </c>
@@ -16562,7 +16480,7 @@
     <row r="102" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9"/>
       <c r="B102" s="42"/>
-      <c r="C102" s="362"/>
+      <c r="C102" s="363"/>
       <c r="D102" s="102" t="s">
         <v>100</v>
       </c>
@@ -16630,7 +16548,7 @@
     <row r="103" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9"/>
       <c r="B103" s="42"/>
-      <c r="C103" s="362"/>
+      <c r="C103" s="363"/>
       <c r="D103" s="102" t="s">
         <v>153</v>
       </c>
@@ -16698,7 +16616,7 @@
     <row r="104" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9"/>
       <c r="B104" s="42"/>
-      <c r="C104" s="362"/>
+      <c r="C104" s="363"/>
       <c r="D104" s="102" t="s">
         <v>155</v>
       </c>
@@ -16769,7 +16687,7 @@
     <row r="105" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9"/>
       <c r="B105" s="42"/>
-      <c r="C105" s="362"/>
+      <c r="C105" s="363"/>
       <c r="D105" s="102" t="s">
         <v>105</v>
       </c>
@@ -16837,7 +16755,7 @@
     <row r="106" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="9"/>
       <c r="B106" s="42"/>
-      <c r="C106" s="362"/>
+      <c r="C106" s="363"/>
       <c r="D106" s="102" t="s">
         <v>137</v>
       </c>
@@ -16908,7 +16826,7 @@
     <row r="107" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9"/>
       <c r="B107" s="42"/>
-      <c r="C107" s="362"/>
+      <c r="C107" s="363"/>
       <c r="D107" s="102" t="s">
         <v>138</v>
       </c>
@@ -16979,7 +16897,7 @@
     <row r="108" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9"/>
       <c r="B108" s="42"/>
-      <c r="C108" s="362"/>
+      <c r="C108" s="363"/>
       <c r="D108" s="102" t="s">
         <v>133</v>
       </c>
@@ -17050,7 +16968,7 @@
     <row r="109" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9"/>
       <c r="B109" s="42"/>
-      <c r="C109" s="362"/>
+      <c r="C109" s="363"/>
       <c r="D109" s="102" t="s">
         <v>142</v>
       </c>
@@ -17118,7 +17036,7 @@
     <row r="110" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9"/>
       <c r="B110" s="42"/>
-      <c r="C110" s="362"/>
+      <c r="C110" s="363"/>
       <c r="D110" s="102" t="s">
         <v>152</v>
       </c>
@@ -17186,7 +17104,7 @@
     <row r="111" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="9"/>
       <c r="B111" s="42"/>
-      <c r="C111" s="362"/>
+      <c r="C111" s="363"/>
       <c r="D111" s="102" t="s">
         <v>115</v>
       </c>
@@ -17254,7 +17172,7 @@
     <row r="112" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="9"/>
       <c r="B112" s="42"/>
-      <c r="C112" s="362"/>
+      <c r="C112" s="363"/>
       <c r="D112" s="102" t="s">
         <v>116</v>
       </c>
@@ -17322,7 +17240,7 @@
     <row r="113" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9"/>
       <c r="B113" s="14"/>
-      <c r="C113" s="362"/>
+      <c r="C113" s="363"/>
       <c r="D113" s="102" t="s">
         <v>118</v>
       </c>
@@ -17390,7 +17308,7 @@
     <row r="114" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="36"/>
       <c r="B114" s="14"/>
-      <c r="C114" s="362"/>
+      <c r="C114" s="363"/>
       <c r="D114" s="102" t="s">
         <v>134</v>
       </c>
@@ -17458,7 +17376,7 @@
     <row r="115" spans="1:61" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9"/>
       <c r="B115" s="14"/>
-      <c r="C115" s="363"/>
+      <c r="C115" s="364"/>
       <c r="D115" s="252" t="s">
         <v>84</v>
       </c>
@@ -17526,7 +17444,7 @@
     <row r="116" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A116" s="9"/>
       <c r="B116" s="14"/>
-      <c r="C116" s="362"/>
+      <c r="C116" s="363"/>
       <c r="D116" s="39" t="s">
         <v>93</v>
       </c>
@@ -17594,7 +17512,7 @@
     <row r="117" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A117" s="9"/>
       <c r="B117" s="14"/>
-      <c r="C117" s="362"/>
+      <c r="C117" s="363"/>
       <c r="D117" s="39" t="s">
         <v>95</v>
       </c>
@@ -17662,7 +17580,7 @@
     <row r="118" spans="1:61" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9"/>
       <c r="B118" s="14"/>
-      <c r="C118" s="363"/>
+      <c r="C118" s="364"/>
       <c r="D118" s="34" t="s">
         <v>143</v>
       </c>
@@ -17867,47 +17785,47 @@
       <c r="E121" s="80"/>
       <c r="F121" s="14"/>
       <c r="G121" s="14"/>
-      <c r="H121" s="369" t="s">
+      <c r="H121" s="358" t="s">
         <v>156</v>
       </c>
-      <c r="I121" s="369"/>
-      <c r="J121" s="369"/>
-      <c r="K121" s="369"/>
-      <c r="L121" s="369"/>
-      <c r="M121" s="369"/>
-      <c r="N121" s="369"/>
-      <c r="O121" s="369"/>
-      <c r="P121" s="369"/>
-      <c r="Q121" s="369"/>
-      <c r="R121" s="369"/>
-      <c r="S121" s="369"/>
-      <c r="T121" s="369"/>
-      <c r="U121" s="369"/>
-      <c r="V121" s="369"/>
-      <c r="W121" s="369"/>
-      <c r="X121" s="369"/>
-      <c r="Y121" s="369"/>
-      <c r="Z121" s="369"/>
-      <c r="AA121" s="369"/>
-      <c r="AB121" s="369"/>
-      <c r="AC121" s="369"/>
-      <c r="AD121" s="369"/>
+      <c r="I121" s="358"/>
+      <c r="J121" s="358"/>
+      <c r="K121" s="358"/>
+      <c r="L121" s="358"/>
+      <c r="M121" s="358"/>
+      <c r="N121" s="358"/>
+      <c r="O121" s="358"/>
+      <c r="P121" s="358"/>
+      <c r="Q121" s="358"/>
+      <c r="R121" s="358"/>
+      <c r="S121" s="358"/>
+      <c r="T121" s="358"/>
+      <c r="U121" s="358"/>
+      <c r="V121" s="358"/>
+      <c r="W121" s="358"/>
+      <c r="X121" s="358"/>
+      <c r="Y121" s="358"/>
+      <c r="Z121" s="358"/>
+      <c r="AA121" s="358"/>
+      <c r="AB121" s="358"/>
+      <c r="AC121" s="358"/>
+      <c r="AD121" s="358"/>
       <c r="AE121" s="218"/>
       <c r="AF121" s="218"/>
-      <c r="AG121" s="367" t="s">
+      <c r="AG121" s="356" t="s">
         <v>119</v>
       </c>
-      <c r="AH121" s="367"/>
-      <c r="AI121" s="367"/>
-      <c r="AJ121" s="367"/>
-      <c r="AK121" s="367"/>
-      <c r="AL121" s="368" t="s">
+      <c r="AH121" s="356"/>
+      <c r="AI121" s="356"/>
+      <c r="AJ121" s="356"/>
+      <c r="AK121" s="356"/>
+      <c r="AL121" s="357" t="s">
         <v>120</v>
       </c>
-      <c r="AM121" s="368"/>
-      <c r="AN121" s="368"/>
-      <c r="AO121" s="368"/>
-      <c r="AP121" s="368"/>
+      <c r="AM121" s="357"/>
+      <c r="AN121" s="357"/>
+      <c r="AO121" s="357"/>
+      <c r="AP121" s="357"/>
       <c r="AQ121" s="123"/>
       <c r="AR121" s="199"/>
       <c r="AS121" s="9"/>
@@ -17917,19 +17835,19 @@
       <c r="AW121" s="9"/>
       <c r="AX121" s="9"/>
       <c r="AY121" s="14"/>
-      <c r="AZ121" s="369" t="s">
+      <c r="AZ121" s="358" t="s">
         <v>102</v>
       </c>
-      <c r="BA121" s="369"/>
-      <c r="BB121" s="369"/>
-      <c r="BC121" s="369"/>
-      <c r="BD121" s="369"/>
-      <c r="BE121" s="368" t="s">
+      <c r="BA121" s="358"/>
+      <c r="BB121" s="358"/>
+      <c r="BC121" s="358"/>
+      <c r="BD121" s="358"/>
+      <c r="BE121" s="357" t="s">
         <v>125</v>
       </c>
-      <c r="BF121" s="368"/>
-      <c r="BG121" s="368"/>
-      <c r="BH121" s="368"/>
+      <c r="BF121" s="357"/>
+      <c r="BG121" s="357"/>
+      <c r="BH121" s="357"/>
       <c r="BI121" s="9"/>
     </row>
     <row r="122" spans="1:61" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -47291,6 +47209,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C51:C56"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="C25:C42"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="C48:C50"/>
     <mergeCell ref="AG121:AK121"/>
     <mergeCell ref="AL121:AP121"/>
     <mergeCell ref="AZ121:BD121"/>
@@ -47301,12 +47225,6 @@
     <mergeCell ref="C89:C115"/>
     <mergeCell ref="C116:C118"/>
     <mergeCell ref="H121:AD121"/>
-    <mergeCell ref="C51:C56"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="C25:C42"/>
-    <mergeCell ref="C43:C47"/>
-    <mergeCell ref="C48:C50"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E53" xr:uid="{4E1141FF-02DB-493C-9A32-9CECACE07768}">
@@ -47319,11 +47237,19 @@
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C14E51DAAF6A9C42A8F1DD865814BDF7" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d88df49d0f8b67e7130da01e27c88464">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="99cb1dfc-2f3f-4d71-a8c2-68e668168860" xmlns:ns3="2ef98288-d855-47c7-ae11-82173b92d2a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5264e82284ae165297613bf56a6eef8d" ns2:_="" ns3:_="">
     <xsd:import namespace="99cb1dfc-2f3f-4d71-a8c2-68e668168860"/>
@@ -47512,15 +47438,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -47533,6 +47450,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213ADA29-AF13-4D3B-BB2D-43EEEED5D0D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E33173B-E23B-46C7-9D57-3AB6F940EE4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47547,14 +47472,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213ADA29-AF13-4D3B-BB2D-43EEEED5D0D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
